--- a/操作説明書.xlsx
+++ b/操作説明書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1335417-E263-4A7B-B11C-FF1E639D533C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A3613D-7A1D-46E5-ACB2-7743050F7BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A6FD4937-72FB-4DAF-9FB3-4DBDD34E90C2}"/>
   </bookViews>
@@ -103,7 +103,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="10115624" cy="5857918"/>
@@ -142,7 +142,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="10163249" cy="5838868"/>
@@ -181,13 +181,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>566737</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>319088</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>119062</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -247,7 +247,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4200556" cy="5038762"/>
@@ -286,13 +286,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>490538</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>180976</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>176213</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -352,7 +352,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5191163" cy="1857389"/>
@@ -391,13 +391,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>633413</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -457,7 +457,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6000794" cy="4438682"/>
@@ -496,13 +496,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>104776</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>395288</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>100013</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -562,13 +562,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">

--- a/操作説明書.xlsx
+++ b/操作説明書.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A3613D-7A1D-46E5-ACB2-7743050F7BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7772ED05-71DB-4C93-ABC9-1576424963D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A6FD4937-72FB-4DAF-9FB3-4DBDD34E90C2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{A6FD4937-72FB-4DAF-9FB3-4DBDD34E90C2}"/>
   </bookViews>
   <sheets>
     <sheet name="アイビスペイント＿メモ" sheetId="1" r:id="rId1"/>
+    <sheet name="xの設定" sheetId="2" r:id="rId2"/>
+    <sheet name="note" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,9 +37,472 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Xには「Xプレミアム」という有料のサブスクリプションサービスがあります</t>
+    <rPh sb="14" eb="16">
+      <t>ユウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本格的にアカウントを伸ばしたいと思ったら課金を検討</t>
+    <rPh sb="0" eb="3">
+      <t>ホンカクテキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カキン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>140字制限が最大25000文字まで拡張される</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リプライが優先的に上位表示される</t>
+    <rPh sb="5" eb="8">
+      <t>ユウセンテキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポストしてから１時間以内に限り、一定回数の内容変更が可能</t>
+    <rPh sb="8" eb="10">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大３時間、最大８GBのビデオ（1080P）をアップロードできる</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前の横に青のチェックマークがつく</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイムラインに表示される広告数の削減</t>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>コウコクスウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収益化がサブスクリプションが可能（条件を満たしている場合）</t>
+    <rPh sb="0" eb="3">
+      <t>シュウエキカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X上でのコミュニティを作成できる</t>
+    <rPh sb="1" eb="2">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※編集したポストは現状伸びにくい傾向があるため、削除して投稿しなおすことがおすすめ</t>
+    <rPh sb="1" eb="3">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケイコウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>トウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※課金する場合はXのアプリからよりもブラウザからのほうが安くなるため、ブラウザからXにアクセスして有料プランに変更</t>
+    <rPh sb="1" eb="3">
+      <t>カキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヤス</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ユウリョウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>身バレ・乗っ取りを防ぐ４つの設定</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>フセ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セキュリティ設定をする</t>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定とプライバシー→セキュリティとアカウントアクセス→セキュリティを選択して２要素認証かパスキーを設定</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「見つけやすさと連絡先」の項目をすべてオフにする</t>
+    <rPh sb="1" eb="2">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>レンラク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「設定とプライバシー」→「プライバシーと安全」→「見つけやすさと連絡先」を選択し、すべての項目をオフにする</t>
+    <rPh sb="1" eb="3">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>アンゼン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>レンラク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誕生日の公開設定を「自分のみ」に変更する</t>
+    <rPh sb="0" eb="3">
+      <t>タンジョウビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のアカウントを開き、「編集」画面を選択。生年月日を選択し、「月日」と「年」を「自分のみ」にする</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>センシティブ設定の解除</t>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「設定とプライバシー」→「プライバシーと安全」を選択。「あなたのポスト」→「あなたがポストする画像／動画はセンシティブな内容を含むものとして設定する」をオフにする</t>
+    <rPh sb="1" eb="3">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>アンゼン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ドウガ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーワードに関する「いいね」が１００以上のポストを検索</t>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（キーワード）min_faves:100</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーワードに関するリポストが50以上のポストを検索</t>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（キーワード）min_retweets:50</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特定のアカウントの特定期間（この例では2025年１月１日から３月３１日まで）のポストを検索</t>
+    <rPh sb="0" eb="2">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>from:（アカウント名） since:2025-01-01 until:2025-03-31</t>
+    <rPh sb="11" eb="12">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://note.com/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NOTE ログイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -48,6 +513,24 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -71,17 +554,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -627,6 +1120,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>409603</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>80988</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F90B597C-1DE1-E318-67DC-374631EFB4AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="223838"/>
+          <a:ext cx="3838603" cy="3438550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -951,4 +1493,185 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{957E3BE1-FF53-45FF-A35C-776147A2808C}">
+  <dimension ref="B2:D37"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.7">
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="C37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C039B8EA-7FAC-4DFF-94FB-E76D1C32651B}">
+  <dimension ref="B18:D18"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetData>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D18" r:id="rId1" xr:uid="{9B8CAAE3-C0BE-4B57-B973-F5A2889A29D6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/操作説明書.xlsx
+++ b/操作説明書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7772ED05-71DB-4C93-ABC9-1576424963D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9139EAD-4655-4DBD-BA74-3A074AC4CD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{A6FD4937-72FB-4DAF-9FB3-4DBDD34E90C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Xには「Xプレミアム」という有料のサブスクリプションサービスがあります</t>
     <rPh sb="14" eb="16">
@@ -495,6 +495,20 @@
   </si>
   <si>
     <t>NOTE ログイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://note.com/pickybig</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←記事投稿するときはこっち</t>
+    <rPh sb="1" eb="3">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウコウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -537,12 +551,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -562,7 +582,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -570,6 +590,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1166,6 +1192,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>108699</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B493C43-9404-6DA4-4FD9-4214CFD30C55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="4700588"/>
+          <a:ext cx="7705725" cy="4585449"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1655,23 +1725,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C039B8EA-7FAC-4DFF-94FB-E76D1C32651B}">
-  <dimension ref="B18:D18"/>
+  <dimension ref="B18:F20"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.7">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B18" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.7">
+      <c r="B20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="D18" r:id="rId1" xr:uid="{9B8CAAE3-C0BE-4B57-B973-F5A2889A29D6}"/>
+    <hyperlink ref="B20" r:id="rId2" xr:uid="{D0D2E5CC-DE2D-430E-BC02-FA087506AA20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>